--- a/data/tsfc_heatmap.xlsx
+++ b/data/tsfc_heatmap.xlsx
@@ -454,7 +454,7 @@
         <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>8.555928824594362e-05</v>
+        <v>9.1751045469332e-05</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         <v>0.2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.972617154232737e-05</v>
+        <v>8.658357652408853e-05</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>7.507147538886194e-05</v>
+        <v>8.226696014641603e-05</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>0.2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.124879918452871e-05</v>
+        <v>7.859676271896518e-05</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>0.2</v>
       </c>
       <c r="C6" t="n">
-        <v>6.803878617191686e-05</v>
+        <v>7.543029059151495e-05</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +509,7 @@
         <v>0.2</v>
       </c>
       <c r="C7" t="n">
-        <v>6.529497273487708e-05</v>
+        <v>7.26647174697228e-05</v>
       </c>
     </row>
     <row r="8">
@@ -520,7 +520,7 @@
         <v>0.2</v>
       </c>
       <c r="C8" t="n">
-        <v>6.291539512145796e-05</v>
+        <v>7.022394280927158e-05</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>6.082662844536452e-05</v>
+        <v>6.86971046054594e-05</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         <v>0.2</v>
       </c>
       <c r="C10" t="n">
-        <v>5.897430051220894e-05</v>
+        <v>6.731578794848645e-05</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>0.2</v>
       </c>
       <c r="C11" t="n">
-        <v>5.731719058375382e-05</v>
+        <v>6.59793298544455e-05</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +564,7 @@
         <v>0.2</v>
       </c>
       <c r="C12" t="n">
-        <v>5.582341563375733e-05</v>
+        <v>6.468575636273234e-05</v>
       </c>
     </row>
     <row r="13">
@@ -575,7 +575,7 @@
         <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>5.446788463410191e-05</v>
+        <v>6.343319889720288e-05</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +586,7 @@
         <v>0.2</v>
       </c>
       <c r="C14" t="n">
-        <v>5.323055135113205e-05</v>
+        <v>6.221988802632836e-05</v>
       </c>
     </row>
     <row r="15">
@@ -594,10 +594,10 @@
         <v>1.4</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C15" t="n">
-        <v>8.162896109419792e-05</v>
+        <v>8.656203239240149e-05</v>
       </c>
     </row>
     <row r="16">
@@ -605,10 +605,10 @@
         <v>1.45</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C16" t="n">
-        <v>7.60624316586944e-05</v>
+        <v>8.157738299945209e-05</v>
       </c>
     </row>
     <row r="17">
@@ -616,10 +616,10 @@
         <v>1.5</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C17" t="n">
-        <v>7.162034723856969e-05</v>
+        <v>7.74236383485297e-05</v>
       </c>
     </row>
     <row r="18">
@@ -627,10 +627,10 @@
         <v>1.55</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C18" t="n">
-        <v>6.797217785451414e-05</v>
+        <v>7.389914485235616e-05</v>
       </c>
     </row>
     <row r="19">
@@ -638,10 +638,10 @@
         <v>1.6</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C19" t="n">
-        <v>6.490861614937213e-05</v>
+        <v>7.08636783501182e-05</v>
       </c>
     </row>
     <row r="20">
@@ -649,10 +649,10 @@
         <v>1.65</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C20" t="n">
-        <v>6.228990804774381e-05</v>
+        <v>6.821651440622034e-05</v>
       </c>
     </row>
     <row r="21">
@@ -660,10 +660,10 @@
         <v>1.7</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C21" t="n">
-        <v>6.00187605071114e-05</v>
+        <v>6.588331282146102e-05</v>
       </c>
     </row>
     <row r="22">
@@ -671,10 +671,10 @@
         <v>1.75</v>
       </c>
       <c r="B22" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C22" t="n">
-        <v>5.802511185246557e-05</v>
+        <v>6.433504744328154e-05</v>
       </c>
     </row>
     <row r="23">
@@ -682,10 +682,10 @@
         <v>1.8</v>
       </c>
       <c r="B23" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C23" t="n">
-        <v>5.625708024518043e-05</v>
+        <v>6.295514041899631e-05</v>
       </c>
     </row>
     <row r="24">
@@ -693,10 +693,10 @@
         <v>1.85</v>
       </c>
       <c r="B24" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C24" t="n">
-        <v>5.467533282509253e-05</v>
+        <v>6.162344841467952e-05</v>
       </c>
     </row>
     <row r="25">
@@ -704,10 +704,10 @@
         <v>1.9</v>
       </c>
       <c r="B25" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C25" t="n">
-        <v>5.32494466929018e-05</v>
+        <v>6.033767235578056e-05</v>
       </c>
     </row>
     <row r="26">
@@ -715,10 +715,10 @@
         <v>1.95</v>
       </c>
       <c r="B26" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C26" t="n">
-        <v>5.195547982557427e-05</v>
+        <v>5.90956477105012e-05</v>
       </c>
     </row>
     <row r="27">
@@ -726,10 +726,10 @@
         <v>2</v>
       </c>
       <c r="B27" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C27" t="n">
-        <v>5.07743039163834e-05</v>
+        <v>5.789533554397648e-05</v>
       </c>
     </row>
     <row r="28">
@@ -737,10 +737,10 @@
         <v>1.4</v>
       </c>
       <c r="B28" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>7.811846724239052e-05</v>
+        <v>8.224076844212689e-05</v>
       </c>
     </row>
     <row r="29">
@@ -748,10 +748,10 @@
         <v>1.45</v>
       </c>
       <c r="B29" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>7.279001044836519e-05</v>
+        <v>7.74065440524852e-05</v>
       </c>
     </row>
     <row r="30">
@@ -759,10 +759,10 @@
         <v>1.5</v>
       </c>
       <c r="B30" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>6.853779488588152e-05</v>
+        <v>7.338740668349469e-05</v>
       </c>
     </row>
     <row r="31">
@@ -770,10 +770,10 @@
         <v>1.55</v>
       </c>
       <c r="B31" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>6.504546435572196e-05</v>
+        <v>6.998368447302634e-05</v>
       </c>
     </row>
     <row r="32">
@@ -781,10 +781,10 @@
         <v>1.6</v>
       </c>
       <c r="B32" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>6.21126864066588e-05</v>
+        <v>6.705702421419896e-05</v>
       </c>
     </row>
     <row r="33">
@@ -792,10 +792,10 @@
         <v>1.65</v>
       </c>
       <c r="B33" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>5.960569908422043e-05</v>
+        <v>6.450834416618936e-05</v>
       </c>
     </row>
     <row r="34">
@@ -803,10 +803,10 @@
         <v>1.7</v>
       </c>
       <c r="B34" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>5.743138061830663e-05</v>
+        <v>6.226470550702598e-05</v>
       </c>
     </row>
     <row r="35">
@@ -814,10 +814,10 @@
         <v>1.75</v>
       </c>
       <c r="B35" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>5.552267290661118e-05</v>
+        <v>6.070653380758298e-05</v>
       </c>
     </row>
     <row r="36">
@@ -825,10 +825,10 @@
         <v>1.8</v>
       </c>
       <c r="B36" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>5.382991815306962e-05</v>
+        <v>5.932853212124012e-05</v>
       </c>
     </row>
     <row r="37">
@@ -836,10 +836,10 @@
         <v>1.85</v>
       </c>
       <c r="B37" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>5.231546948222855e-05</v>
+        <v>5.800185980161787e-05</v>
       </c>
     </row>
     <row r="38">
@@ -847,10 +847,10 @@
         <v>1.9</v>
       </c>
       <c r="B38" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>5.095020796583081e-05</v>
+        <v>5.672389236188328e-05</v>
       </c>
     </row>
     <row r="39">
@@ -858,10 +858,10 @@
         <v>1.95</v>
       </c>
       <c r="B39" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>4.971121770061248e-05</v>
+        <v>5.549217143924869e-05</v>
       </c>
     </row>
     <row r="40">
@@ -869,10 +869,10 @@
         <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>4.858019013053828e-05</v>
+        <v>5.430439265089707e-05</v>
       </c>
     </row>
     <row r="41">
@@ -880,10 +880,10 @@
         <v>1.4</v>
       </c>
       <c r="B41" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C41" t="n">
-        <v>7.495797654127514e-05</v>
+        <v>7.856012168318774e-05</v>
       </c>
     </row>
     <row r="42">
@@ -891,10 +891,10 @@
         <v>1.45</v>
       </c>
       <c r="B42" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C42" t="n">
-        <v>6.984382479984071e-05</v>
+        <v>7.385280072293629e-05</v>
       </c>
     </row>
     <row r="43">
@@ -902,10 +902,10 @@
         <v>1.5</v>
       </c>
       <c r="B43" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C43" t="n">
-        <v>6.576252166349549e-05</v>
+        <v>6.994769386546373e-05</v>
       </c>
     </row>
     <row r="44">
@@ -913,10 +913,10 @@
         <v>1.55</v>
       </c>
       <c r="B44" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C44" t="n">
-        <v>6.241047025888369e-05</v>
+        <v>6.664655365985922e-05</v>
       </c>
     </row>
     <row r="45">
@@ -924,10 +924,10 @@
         <v>1.6</v>
       </c>
       <c r="B45" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C45" t="n">
-        <v>5.959541736172184e-05</v>
+        <v>6.381247700523734e-05</v>
       </c>
     </row>
     <row r="46">
@@ -935,10 +935,10 @@
         <v>1.65</v>
       </c>
       <c r="B46" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C46" t="n">
-        <v>5.718899511554163e-05</v>
+        <v>6.134770000291622e-05</v>
       </c>
     </row>
     <row r="47">
@@ -946,10 +946,10 @@
         <v>1.7</v>
       </c>
       <c r="B47" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C47" t="n">
-        <v>5.510183670705197e-05</v>
+        <v>5.918042991623477e-05</v>
       </c>
     </row>
     <row r="48">
@@ -957,10 +957,10 @@
         <v>1.75</v>
       </c>
       <c r="B48" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C48" t="n">
-        <v>5.326958782056286e-05</v>
+        <v>5.761975788414582e-05</v>
       </c>
     </row>
     <row r="49">
@@ -968,10 +968,10 @@
         <v>1.8</v>
       </c>
       <c r="B49" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C49" t="n">
-        <v>5.164459271357606e-05</v>
+        <v>5.624420977971962e-05</v>
       </c>
     </row>
     <row r="50">
@@ -979,10 +979,10 @@
         <v>1.85</v>
       </c>
       <c r="B50" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C50" t="n">
-        <v>5.019072220443386e-05</v>
+        <v>5.492288804033914e-05</v>
       </c>
     </row>
     <row r="51">
@@ -990,10 +990,10 @@
         <v>1.9</v>
       </c>
       <c r="B51" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C51" t="n">
-        <v>4.888003117228882e-05</v>
+        <v>5.365284430458266e-05</v>
       </c>
     </row>
     <row r="52">
@@ -1001,10 +1001,10 @@
         <v>1.95</v>
       </c>
       <c r="B52" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C52" t="n">
-        <v>4.769052739930126e-05</v>
+        <v>5.243132998899424e-05</v>
       </c>
     </row>
     <row r="53">
@@ -1012,10 +1012,10 @@
         <v>2</v>
       </c>
       <c r="B53" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="C53" t="n">
-        <v>4.660464024553078e-05</v>
+        <v>5.125578047589813e-05</v>
       </c>
     </row>
     <row r="54">
@@ -1023,10 +1023,10 @@
         <v>1.4</v>
       </c>
       <c r="B54" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>7.209294485566059e-05</v>
+        <v>7.536859670710844e-05</v>
       </c>
     </row>
     <row r="55">
@@ -1034,10 +1034,10 @@
         <v>1.45</v>
       </c>
       <c r="B55" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>6.717303879039368e-05</v>
+        <v>7.077053920561562e-05</v>
       </c>
     </row>
     <row r="56">
@@ -1045,10 +1045,10 @@
         <v>1.5</v>
       </c>
       <c r="B56" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>6.324664948900949e-05</v>
+        <v>6.696398519754062e-05</v>
       </c>
     </row>
     <row r="57">
@@ -1056,10 +1056,10 @@
         <v>1.55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>6.00217455275568e-05</v>
+        <v>6.375171303537753e-05</v>
       </c>
     </row>
     <row r="58">
@@ -1067,10 +1067,10 @@
         <v>1.6</v>
       </c>
       <c r="B58" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>5.73133969207189e-05</v>
+        <v>6.099796590022573e-05</v>
       </c>
     </row>
     <row r="59">
@@ -1078,10 +1078,10 @@
         <v>1.65</v>
       </c>
       <c r="B59" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>5.499812515203629e-05</v>
+        <v>5.860606138121415e-05</v>
       </c>
     </row>
     <row r="60">
@@ -1089,10 +1089,10 @@
         <v>1.7</v>
       </c>
       <c r="B60" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>5.298996697912799e-05</v>
+        <v>5.650516588414433e-05</v>
       </c>
     </row>
     <row r="61">
@@ -1100,10 +1100,10 @@
         <v>1.75</v>
       </c>
       <c r="B61" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C61" t="n">
-        <v>5.122701884250974e-05</v>
+        <v>5.494690454568449e-05</v>
       </c>
     </row>
     <row r="62">
@@ -1111,10 +1111,10 @@
         <v>1.8</v>
       </c>
       <c r="B62" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C62" t="n">
-        <v>4.966343968866271e-05</v>
+        <v>5.357437044956347e-05</v>
       </c>
     </row>
     <row r="63">
@@ -1122,10 +1122,10 @@
         <v>1.85</v>
       </c>
       <c r="B63" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C63" t="n">
-        <v>4.826447598654814e-05</v>
+        <v>5.225876158924746e-05</v>
       </c>
     </row>
     <row r="64">
@@ -1133,10 +1133,10 @@
         <v>1.9</v>
       </c>
       <c r="B64" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>4.700324656163746e-05</v>
+        <v>5.09968087879278e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1144,10 +1144,10 @@
         <v>1.95</v>
       </c>
       <c r="B65" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>4.585859642637004e-05</v>
+        <v>4.978547805140448e-05</v>
       </c>
     </row>
     <row r="66">
@@ -1155,10 +1155,10 @@
         <v>2</v>
       </c>
       <c r="B66" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>4.481362378652506e-05</v>
+        <v>4.862195064440141e-05</v>
       </c>
     </row>
     <row r="67">
@@ -1166,10 +1166,10 @@
         <v>1.4</v>
       </c>
       <c r="B67" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C67" t="n">
-        <v>6.948006513138471e-05</v>
+        <v>7.256080419007442e-05</v>
       </c>
     </row>
     <row r="68">
@@ -1177,10 +1177,10 @@
         <v>1.45</v>
       </c>
       <c r="B68" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C68" t="n">
-        <v>6.473728959405112e-05</v>
+        <v>6.805842912259703e-05</v>
       </c>
     </row>
     <row r="69">
@@ -1188,10 +1188,10 @@
         <v>1.5</v>
       </c>
       <c r="B69" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C69" t="n">
-        <v>6.09521639749379e-05</v>
+        <v>6.433847203495056e-05</v>
       </c>
     </row>
     <row r="70">
@@ -1199,10 +1199,10 @@
         <v>1.55</v>
       </c>
       <c r="B70" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C70" t="n">
-        <v>5.78432035695747e-05</v>
+        <v>6.120444706007234e-05</v>
       </c>
     </row>
     <row r="71">
@@ -1210,10 +1210,10 @@
         <v>1.6</v>
       </c>
       <c r="B71" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C71" t="n">
-        <v>5.523215654712695e-05</v>
+        <v>5.852151993916703e-05</v>
       </c>
     </row>
     <row r="72">
@@ -1221,10 +1221,10 @@
         <v>1.65</v>
       </c>
       <c r="B72" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C72" t="n">
-        <v>5.300000302692503e-05</v>
+        <v>5.619391400380511e-05</v>
       </c>
     </row>
     <row r="73">
@@ -1232,10 +1232,10 @@
         <v>1.7</v>
       </c>
       <c r="B73" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C73" t="n">
-        <v>5.106388350231025e-05</v>
+        <v>5.415161470680796e-05</v>
       </c>
     </row>
     <row r="74">
@@ -1243,10 +1243,10 @@
         <v>1.75</v>
       </c>
       <c r="B74" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C74" t="n">
-        <v>4.936412926659418e-05</v>
+        <v>5.259909806247409e-05</v>
       </c>
     </row>
     <row r="75">
@@ -1254,10 +1254,10 @@
         <v>1.8</v>
       </c>
       <c r="B75" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C75" t="n">
-        <v>4.785655407822613e-05</v>
+        <v>5.123012531832846e-05</v>
       </c>
     </row>
     <row r="76">
@@ -1265,10 +1265,10 @@
         <v>1.85</v>
       </c>
       <c r="B76" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C76" t="n">
-        <v>4.65076588575506e-05</v>
+        <v>4.992059435988982e-05</v>
       </c>
     </row>
     <row r="77">
@@ -1276,10 +1276,10 @@
         <v>1.9</v>
       </c>
       <c r="B77" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C77" t="n">
-        <v>4.529153263366093e-05</v>
+        <v>4.866691949945748e-05</v>
       </c>
     </row>
     <row r="78">
@@ -1287,10 +1287,10 @@
         <v>1.95</v>
       </c>
       <c r="B78" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C78" t="n">
-        <v>4.418778388081308e-05</v>
+        <v>4.746578709304418e-05</v>
       </c>
     </row>
     <row r="79">
@@ -1298,10 +1298,10 @@
         <v>2</v>
       </c>
       <c r="B79" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="C79" t="n">
-        <v>4.318012071513232e-05</v>
+        <v>4.631413109099984e-05</v>
       </c>
     </row>
     <row r="80">
@@ -1309,10 +1309,10 @@
         <v>1.4</v>
       </c>
       <c r="B80" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C80" t="n">
-        <v>6.708445518483099e-05</v>
+        <v>7.006087782180903e-05</v>
       </c>
     </row>
     <row r="81">
@@ -1320,10 +1320,10 @@
         <v>1.45</v>
       </c>
       <c r="B81" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C81" t="n">
-        <v>6.250406630881797e-05</v>
+        <v>6.564349843105523e-05</v>
       </c>
     </row>
     <row r="82">
@@ -1331,10 +1331,10 @@
         <v>1.5</v>
       </c>
       <c r="B82" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C82" t="n">
-        <v>5.88484456411481e-05</v>
+        <v>6.200069594943385e-05</v>
       </c>
     </row>
     <row r="83">
@@ -1342,10 +1342,10 @@
         <v>1.55</v>
       </c>
       <c r="B83" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C83" t="n">
-        <v>5.584577752657145e-05</v>
+        <v>5.893650688479236e-05</v>
       </c>
     </row>
     <row r="84">
@@ -1353,10 +1353,10 @@
         <v>1.6</v>
       </c>
       <c r="B84" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C84" t="n">
-        <v>5.332393253276652e-05</v>
+        <v>5.631685234644049e-05</v>
       </c>
     </row>
     <row r="85">
@@ -1364,10 +1364,10 @@
         <v>1.65</v>
       </c>
       <c r="B85" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C85" t="n">
-        <v>5.116797835418423e-05</v>
+        <v>5.404672848036372e-05</v>
       </c>
     </row>
     <row r="86">
@@ -1375,10 +1375,10 @@
         <v>1.7</v>
       </c>
       <c r="B86" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C86" t="n">
-        <v>4.929790090807537e-05</v>
+        <v>5.205683282439897e-05</v>
       </c>
     </row>
     <row r="87">
@@ -1386,10 +1386,10 @@
         <v>1.75</v>
       </c>
       <c r="B87" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C87" t="n">
-        <v>4.765608033623864e-05</v>
+        <v>5.051236307972411e-05</v>
       </c>
     </row>
     <row r="88">
@@ -1397,10 +1397,10 @@
         <v>1.8</v>
       </c>
       <c r="B88" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C88" t="n">
-        <v>4.619984747566991e-05</v>
+        <v>4.914747122547341e-05</v>
       </c>
     </row>
     <row r="89">
@@ -1408,10 +1408,10 @@
         <v>1.85</v>
       </c>
       <c r="B89" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C89" t="n">
-        <v>4.489685328279482e-05</v>
+        <v>4.784436890621519e-05</v>
       </c>
     </row>
     <row r="90">
@@ -1419,10 +1419,10 @@
         <v>1.9</v>
       </c>
       <c r="B90" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C90" t="n">
-        <v>4.372207623351273e-05</v>
+        <v>4.659915923612984e-05</v>
       </c>
     </row>
     <row r="91">
@@ -1430,10 +1430,10 @@
         <v>1.95</v>
       </c>
       <c r="B91" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C91" t="n">
-        <v>4.26558247115315e-05</v>
+        <v>4.540825542291442e-05</v>
       </c>
     </row>
     <row r="92">
@@ -1441,10 +1441,10 @@
         <v>2</v>
       </c>
       <c r="B92" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="C92" t="n">
-        <v>4.168236597188185e-05</v>
+        <v>4.426835140940052e-05</v>
       </c>
     </row>
     <row r="93">
@@ -1452,10 +1452,10 @@
         <v>1.4</v>
       </c>
       <c r="B93" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C93" t="n">
-        <v>6.487765978269778e-05</v>
+        <v>6.781263223101591e-05</v>
       </c>
     </row>
     <row r="94">
@@ -1463,10 +1463,10 @@
         <v>1.45</v>
       </c>
       <c r="B94" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C94" t="n">
-        <v>6.044684784107463e-05</v>
+        <v>6.34716822133005e-05</v>
       </c>
     </row>
     <row r="95">
@@ -1474,10 +1474,10 @@
         <v>1.5</v>
       </c>
       <c r="B95" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C95" t="n">
-        <v>5.691051610988166e-05</v>
+        <v>5.9898435707835e-05</v>
       </c>
     </row>
     <row r="96">
@@ -1485,10 +1485,10 @@
         <v>1.55</v>
       </c>
       <c r="B96" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C96" t="n">
-        <v>5.400575538659427e-05</v>
+        <v>5.689729358346113e-05</v>
       </c>
     </row>
     <row r="97">
@@ -1496,10 +1496,10 @@
         <v>1.6</v>
       </c>
       <c r="B97" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C97" t="n">
-        <v>5.156607574344492e-05</v>
+        <v>5.433480603528174e-05</v>
       </c>
     </row>
     <row r="98">
@@ -1507,10 +1507,10 @@
         <v>1.65</v>
       </c>
       <c r="B98" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C98" t="n">
-        <v>4.948031003840945e-05</v>
+        <v>5.211664011721057e-05</v>
       </c>
     </row>
     <row r="99">
@@ -1518,10 +1518,10 @@
         <v>1.7</v>
       </c>
       <c r="B99" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C99" t="n">
-        <v>4.767106517199875e-05</v>
+        <v>5.017412252961669e-05</v>
       </c>
     </row>
     <row r="100">
@@ -1529,10 +1529,10 @@
         <v>1.75</v>
       </c>
       <c r="B100" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C100" t="n">
-        <v>4.608260851742261e-05</v>
+        <v>4.863930697510829e-05</v>
       </c>
     </row>
     <row r="101">
@@ -1540,10 +1540,10 @@
         <v>1.8</v>
       </c>
       <c r="B101" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C101" t="n">
-        <v>4.467366831880938e-05</v>
+        <v>4.727897986481116e-05</v>
       </c>
     </row>
     <row r="102">
@@ -1551,10 +1551,10 @@
         <v>1.85</v>
       </c>
       <c r="B102" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C102" t="n">
-        <v>4.341295484663684e-05</v>
+        <v>4.598263311491373e-05</v>
       </c>
     </row>
     <row r="103">
@@ -1562,10 +1562,10 @@
         <v>1.9</v>
       </c>
       <c r="B103" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C103" t="n">
-        <v>4.227626585469281e-05</v>
+        <v>4.474606476116662e-05</v>
       </c>
     </row>
     <row r="104">
@@ -1573,10 +1573,10 @@
         <v>1.95</v>
       </c>
       <c r="B104" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C104" t="n">
-        <v>4.124455441978643e-05</v>
+        <v>4.356542192871648e-05</v>
       </c>
     </row>
     <row r="105">
@@ -1584,10 +1584,10 @@
         <v>2</v>
       </c>
       <c r="B105" t="n">
-        <v>0.9000000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="C105" t="n">
-        <v>4.030260282264606e-05</v>
+        <v>4.243716621311586e-05</v>
       </c>
     </row>
     <row r="106">
@@ -1595,10 +1595,10 @@
         <v>1.4</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C106" t="n">
-        <v>6.283620256180962e-05</v>
+        <v>6.577344972444197e-05</v>
       </c>
     </row>
     <row r="107">
@@ -1606,10 +1606,10 @@
         <v>1.45</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C107" t="n">
-        <v>5.85437532815016e-05</v>
+        <v>6.150195214949958e-05</v>
       </c>
     </row>
     <row r="108">
@@ -1617,10 +1617,10 @@
         <v>1.5</v>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C108" t="n">
-        <v>5.511776703706972e-05</v>
+        <v>5.799204675122743e-05</v>
       </c>
     </row>
     <row r="109">
@@ -1628,10 +1628,10 @@
         <v>1.55</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C109" t="n">
-        <v>5.23035733932875e-05</v>
+        <v>5.504838161650297e-05</v>
       </c>
     </row>
     <row r="110">
@@ -1639,10 +1639,10 @@
         <v>1.6</v>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C110" t="n">
-        <v>4.993989914626533e-05</v>
+        <v>5.253803995702558e-05</v>
       </c>
     </row>
     <row r="111">
@@ -1650,10 +1650,10 @@
         <v>1.65</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C111" t="n">
-        <v>4.791906004174959e-05</v>
+        <v>5.036728077824089e-05</v>
       </c>
     </row>
     <row r="112">
@@ -1661,10 +1661,10 @@
         <v>1.7</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C112" t="n">
-        <v>4.616608746017711e-05</v>
+        <v>4.846799483170324e-05</v>
       </c>
     </row>
     <row r="113">
@@ -1672,10 +1672,10 @@
         <v>1.75</v>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C113" t="n">
-        <v>4.462699451215372e-05</v>
+        <v>4.694396108172146e-05</v>
       </c>
     </row>
     <row r="114">
@@ -1683,10 +1683,10 @@
         <v>1.8</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C114" t="n">
-        <v>4.3261802073789e-05</v>
+        <v>4.558864331858039e-05</v>
       </c>
     </row>
     <row r="115">
@@ -1694,10 +1694,10 @@
         <v>1.85</v>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C115" t="n">
-        <v>4.204020030242855e-05</v>
+        <v>4.429935044133587e-05</v>
       </c>
     </row>
     <row r="116">
@@ -1705,10 +1705,10 @@
         <v>1.9</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C116" t="n">
-        <v>4.093874479896902e-05</v>
+        <v>4.307158216363597e-05</v>
       </c>
     </row>
     <row r="117">
@@ -1716,10 +1716,10 @@
         <v>1.95</v>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C117" t="n">
-        <v>3.993898499137423e-05</v>
+        <v>4.190122701149868e-05</v>
       </c>
     </row>
     <row r="118">
@@ -1727,10 +1727,10 @@
         <v>2</v>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="C118" t="n">
-        <v>3.902617956586302e-05</v>
+        <v>4.078452212400037e-05</v>
       </c>
     </row>
     <row r="119">
@@ -1738,10 +1738,10 @@
         <v>1.4</v>
       </c>
       <c r="B119" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C119" t="n">
-        <v>6.094051762432513e-05</v>
+        <v>6.391033557025414e-05</v>
       </c>
     </row>
     <row r="120">
@@ -1749,10 +1749,10 @@
         <v>1.45</v>
       </c>
       <c r="B120" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C120" t="n">
-        <v>5.677654618112719e-05</v>
+        <v>5.970252823743676e-05</v>
       </c>
     </row>
     <row r="121">
@@ -1760,10 +1760,10 @@
         <v>1.5</v>
       </c>
       <c r="B121" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C121" t="n">
-        <v>5.345302234428834e-05</v>
+        <v>5.625080827915969e-05</v>
       </c>
     </row>
     <row r="122">
@@ -1771,10 +1771,10 @@
         <v>1.55</v>
       </c>
       <c r="B122" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C122" t="n">
-        <v>5.072292586916768e-05</v>
+        <v>5.335998450817681e-05</v>
       </c>
     </row>
     <row r="123">
@@ -1782,10 +1782,10 @@
         <v>1.6</v>
       </c>
       <c r="B123" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C123" t="n">
-        <v>4.842982758023766e-05</v>
+        <v>5.089759978058404e-05</v>
       </c>
     </row>
     <row r="124">
@@ -1793,10 +1793,10 @@
         <v>1.65</v>
       </c>
       <c r="B124" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C124" t="n">
-        <v>4.646927728195286e-05</v>
+        <v>4.877044336893907e-05</v>
       </c>
     </row>
     <row r="125">
@@ -1804,10 +1804,10 @@
         <v>1.7</v>
       </c>
       <c r="B125" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C125" t="n">
-        <v>4.476855761400659e-05</v>
+        <v>4.691091840503949e-05</v>
       </c>
     </row>
     <row r="126">
@@ -1815,10 +1815,10 @@
         <v>1.75</v>
       </c>
       <c r="B126" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C126" t="n">
-        <v>4.327530269553862e-05</v>
+        <v>4.539845593603501e-05</v>
       </c>
     </row>
     <row r="127">
@@ -1826,10 +1826,10 @@
         <v>1.8</v>
       </c>
       <c r="B127" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C127" t="n">
-        <v>4.195073367702188e-05</v>
+        <v>4.404855196764758e-05</v>
       </c>
     </row>
     <row r="128">
@@ -1837,10 +1837,10 @@
         <v>1.85</v>
       </c>
       <c r="B128" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C128" t="n">
-        <v>4.076545058753901e-05</v>
+        <v>4.276658073349346e-05</v>
       </c>
     </row>
     <row r="129">
@@ -1848,10 +1848,10 @@
         <v>1.9</v>
       </c>
       <c r="B129" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C129" t="n">
-        <v>3.969671272437253e-05</v>
+        <v>4.15477508744305e-05</v>
       </c>
     </row>
     <row r="130">
@@ -1859,10 +1859,10 @@
         <v>1.95</v>
       </c>
       <c r="B130" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C130" t="n">
-        <v>3.872662325308079e-05</v>
+        <v>4.038770009684975e-05</v>
       </c>
     </row>
     <row r="131">
@@ -1870,10 +1870,10 @@
         <v>2</v>
       </c>
       <c r="B131" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="C131" t="n">
-        <v>3.784088322264717e-05</v>
+        <v>3.928244910487398e-05</v>
       </c>
     </row>
     <row r="132">
@@ -1881,10 +1881,10 @@
         <v>1.4</v>
       </c>
       <c r="B132" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C132" t="n">
-        <v>5.917414859387039e-05</v>
+        <v>6.219728871324808e-05</v>
       </c>
     </row>
     <row r="133">
@@ -1892,10 +1892,10 @@
         <v>1.45</v>
       </c>
       <c r="B133" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C133" t="n">
-        <v>5.512988809752807e-05</v>
+        <v>5.80483535659269e-05</v>
       </c>
     </row>
     <row r="134">
@@ -1903,10 +1903,10 @@
         <v>1.5</v>
       </c>
       <c r="B134" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C134" t="n">
-        <v>5.190183524189214e-05</v>
+        <v>5.465048807076794e-05</v>
       </c>
     </row>
     <row r="135">
@@ -1914,10 +1914,10 @@
         <v>1.55</v>
       </c>
       <c r="B135" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C135" t="n">
-        <v>4.925009791772089e-05</v>
+        <v>5.180859857311789e-05</v>
       </c>
     </row>
     <row r="136">
@@ -1925,10 +1925,10 @@
         <v>1.6</v>
       </c>
       <c r="B136" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C136" t="n">
-        <v>4.702276041007318e-05</v>
+        <v>4.939063148619563e-05</v>
       </c>
     </row>
     <row r="137">
@@ -1936,10 +1936,10 @@
         <v>1.65</v>
       </c>
       <c r="B137" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C137" t="n">
-        <v>4.511838587543861e-05</v>
+        <v>4.730385785978537e-05</v>
       </c>
     </row>
     <row r="138">
@@ -1947,10 +1947,10 @@
         <v>1.7</v>
       </c>
       <c r="B138" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C138" t="n">
-        <v>4.346635457539047e-05</v>
+        <v>4.548115182260452e-05</v>
       </c>
     </row>
     <row r="139">
@@ -1958,10 +1958,10 @@
         <v>1.75</v>
       </c>
       <c r="B139" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C139" t="n">
-        <v>4.201581100835131e-05</v>
+        <v>4.398080740787393e-05</v>
       </c>
     </row>
     <row r="140">
@@ -1969,10 +1969,10 @@
         <v>1.8</v>
       </c>
       <c r="B140" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C140" t="n">
-        <v>4.072909467991196e-05</v>
+        <v>4.263668222939981e-05</v>
       </c>
     </row>
     <row r="141">
@@ -1980,10 +1980,10 @@
         <v>1.85</v>
       </c>
       <c r="B141" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C141" t="n">
-        <v>3.957765339267187e-05</v>
+        <v>4.136226974863139e-05</v>
       </c>
     </row>
     <row r="142">
@@ -1991,10 +1991,10 @@
         <v>1.9</v>
       </c>
       <c r="B142" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C142" t="n">
-        <v>3.853940211063165e-05</v>
+        <v>4.015249515493168e-05</v>
       </c>
     </row>
     <row r="143">
@@ -2002,10 +2002,10 @@
         <v>1.95</v>
       </c>
       <c r="B143" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C143" t="n">
-        <v>3.759695994268568e-05</v>
+        <v>3.900275331012908e-05</v>
       </c>
     </row>
     <row r="144">
@@ -2013,10 +2013,10 @@
         <v>2</v>
       </c>
       <c r="B144" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C144" t="n">
-        <v>3.673644010684598e-05</v>
+        <v>3.790885655486902e-05</v>
       </c>
     </row>
   </sheetData>
